--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\JKR\workspace\DataDrivenAutomation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DataDriven\Cloned\DataDriven-by-Jagadeesh\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD38D4BA-81E0-4940-8FE8-8268D43D52E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020" activeTab="1" xr2:uid="{12D5677F-2371-4BBF-AFB2-9F1B56773DFF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="14020"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>uname1</t>
   </si>
@@ -52,34 +50,16 @@
     <t>pass4</t>
   </si>
   <si>
-    <t>firstname1</t>
-  </si>
-  <si>
-    <t>lastname1</t>
-  </si>
-  <si>
-    <t>firstname2</t>
-  </si>
-  <si>
-    <t>lastname2</t>
-  </si>
-  <si>
-    <t>firstname3</t>
-  </si>
-  <si>
-    <t>lastname3</t>
-  </si>
-  <si>
-    <t>firstname4</t>
-  </si>
-  <si>
-    <t>lastname4</t>
+    <t>username</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -430,95 +410,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F23D7CA0-1C26-4B82-A3AE-0F5ED39AFF48}">
-  <dimension ref="A1:B4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B5" t="s">
         <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5DF79C9-DAE8-4F96-88BD-506778DCD9BC}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1">
-        <v>12345</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2">
-        <v>12346</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3">
-        <v>12347</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4">
-        <v>12348</v>
       </c>
     </row>
   </sheetData>
